--- a/datos-referencia/clientes_credito.xlsx
+++ b/datos-referencia/clientes_credito.xlsx
@@ -137,16 +137,8 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="2">
+  <fonts count="1">
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
@@ -162,7 +154,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -170,30 +162,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -492,25 +466,25 @@
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:7">
-      <c r="A1" s="1" t="s">
+      <c r="A1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="F1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="G1" t="s">
         <v>6</v>
       </c>
     </row>
@@ -534,7 +508,7 @@
         <v>50000</v>
       </c>
       <c r="G2">
-        <v>12450</v>
+        <v>47800</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -557,7 +531,7 @@
         <v>30000</v>
       </c>
       <c r="G3">
-        <v>8200.5</v>
+        <v>8200</v>
       </c>
     </row>
     <row r="4" spans="1:7">

--- a/datos-referencia/clientes_credito.xlsx
+++ b/datos-referencia/clientes_credito.xlsx
@@ -413,13 +413,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G1"/>
+  <dimension ref="A1:G9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>cliente</t>
+          <t>nombre_cliente</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
@@ -450,6 +450,254 @@
       <c r="G1" t="inlineStr">
         <is>
           <t>telefono</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Telefonica España SAU</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>A28015865</t>
+        </is>
+      </c>
+      <c r="C2" t="n">
+        <v>50000</v>
+      </c>
+      <c r="D2" t="n">
+        <v>8050</v>
+      </c>
+      <c r="E2" t="n">
+        <v>60</v>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>cuentas@telefonica.com</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>+34 900 123 456</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Repsol Comercial de Productos</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>A28003119</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>30000</v>
+      </c>
+      <c r="D3" t="n">
+        <v>1600</v>
+      </c>
+      <c r="E3" t="n">
+        <v>30</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>facturas@repsol.com</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>+34 900 100 100</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Viajes El Corte Inglés</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>A28229813</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>40000</v>
+      </c>
+      <c r="D4" t="n">
+        <v>11670</v>
+      </c>
+      <c r="E4" t="n">
+        <v>30</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>grupos@viajeseci.es</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>+34 91 418 88 00</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Accenture SLU</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>B82498650</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>45000</v>
+      </c>
+      <c r="D5" t="n">
+        <v>2370</v>
+      </c>
+      <c r="E5" t="n">
+        <v>60</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>ap@accenture.com</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>+34 91 596 60 00</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Deloitte Advisory SL</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>B82850638</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>35000</v>
+      </c>
+      <c r="D6" t="n">
+        <v>4000</v>
+      </c>
+      <c r="E6" t="n">
+        <v>30</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>invoices@deloitte.es</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>+34 91 514 50 00</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Barceló Viajes SL</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>A07004569</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>60000</v>
+      </c>
+      <c r="D7" t="n">
+        <v>10600</v>
+      </c>
+      <c r="E7" t="n">
+        <v>30</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>admin@barcelo.com</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>+34 971 17 71 77</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>KPMG Asesores SL</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>B82498392</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>40000</v>
+      </c>
+      <c r="D8" t="n">
+        <v>1480</v>
+      </c>
+      <c r="E8" t="n">
+        <v>60</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>billing@kpmg.es</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>+34 91 456 34 00</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>McKinsey &amp; Company</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>W0042868B</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>55000</v>
+      </c>
+      <c r="D9" t="n">
+        <v>2200</v>
+      </c>
+      <c r="E9" t="n">
+        <v>45</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>europe.billing@mckinsey.com</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>+34 91 310 82 00</t>
         </is>
       </c>
     </row>

--- a/datos-referencia/clientes_credito.xlsx
+++ b/datos-referencia/clientes_credito.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7" uniqueCount="7">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6" uniqueCount="6">
   <si>
     <t>nombre_cliente</t>
   </si>
@@ -32,9 +32,6 @@
   </si>
   <si>
     <t>email</t>
-  </si>
-  <si>
-    <t>telefono</t>
   </si>
 </sst>
 </file>
@@ -392,10 +389,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G1"/>
+  <dimension ref="A1:F1"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:7">
+    <row r="1" spans="1:6">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -413,9 +410,6 @@
       </c>
       <c r="F1" s="1" t="s">
         <v>5</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>6</v>
       </c>
     </row>
   </sheetData>
